--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745160</v>
+        <v>122745155</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>79872</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorp SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720387</v>
+        <v>720365</v>
       </c>
       <c r="R2" t="n">
-        <v>7138560</v>
+        <v>7138578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122745138</v>
       </c>
       <c r="B3" t="n">
-        <v>92146</v>
+        <v>92249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745155</v>
+        <v>122745160</v>
       </c>
       <c r="B4" t="n">
-        <v>79770</v>
+        <v>90958</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Tjuttorp SÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720365</v>
+        <v>720387</v>
       </c>
       <c r="R4" t="n">
-        <v>7138578</v>
+        <v>7138560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745155</v>
+        <v>122745160</v>
       </c>
       <c r="B2" t="n">
-        <v>79872</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Tjuttorp SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720365</v>
+        <v>720387</v>
       </c>
       <c r="R2" t="n">
-        <v>7138578</v>
+        <v>7138560</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122745138</v>
       </c>
       <c r="B3" t="n">
-        <v>92249</v>
+        <v>92253</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745160</v>
+        <v>122745155</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjuttorp SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720387</v>
+        <v>720365</v>
       </c>
       <c r="R4" t="n">
-        <v>7138560</v>
+        <v>7138578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745160</v>
+        <v>122745155</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorp SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720387</v>
+        <v>720365</v>
       </c>
       <c r="R2" t="n">
-        <v>7138560</v>
+        <v>7138578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745155</v>
+        <v>122745160</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Tjuttorp SÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720365</v>
+        <v>720387</v>
       </c>
       <c r="R4" t="n">
-        <v>7138578</v>
+        <v>7138560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745138</v>
+        <v>122745160</v>
       </c>
       <c r="B3" t="n">
-        <v>92253</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill- SÖ, Vb</t>
+          <t>Tjuttorp SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720390</v>
+        <v>720387</v>
       </c>
       <c r="R3" t="n">
-        <v>7138467</v>
+        <v>7138560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745160</v>
+        <v>122745138</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>92253</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjuttorp SÖ, Vb</t>
+          <t>Lill- SÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720387</v>
+        <v>720390</v>
       </c>
       <c r="R4" t="n">
-        <v>7138560</v>
+        <v>7138467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745155</v>
+        <v>122745160</v>
       </c>
       <c r="B2" t="n">
-        <v>79876</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Tjuttorp SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720365</v>
+        <v>720387</v>
       </c>
       <c r="R2" t="n">
-        <v>7138578</v>
+        <v>7138560</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745160</v>
+        <v>122745155</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjuttorp SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720387</v>
+        <v>720365</v>
       </c>
       <c r="R3" t="n">
-        <v>7138560</v>
+        <v>7138578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745160</v>
+        <v>122745155</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorp SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720387</v>
+        <v>720365</v>
       </c>
       <c r="R2" t="n">
-        <v>7138560</v>
+        <v>7138578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745155</v>
+        <v>122745160</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Tjuttorp SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720365</v>
+        <v>720387</v>
       </c>
       <c r="R3" t="n">
-        <v>7138578</v>
+        <v>7138560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745160</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745155</v>
+        <v>122745138</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>92261</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Lill- SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720365</v>
+        <v>720390</v>
       </c>
       <c r="R3" t="n">
-        <v>7138578</v>
+        <v>7138467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745138</v>
+        <v>122745155</v>
       </c>
       <c r="B4" t="n">
-        <v>92253</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill- SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720390</v>
+        <v>720365</v>
       </c>
       <c r="R4" t="n">
-        <v>7138467</v>
+        <v>7138578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745138</v>
+        <v>122745155</v>
       </c>
       <c r="B3" t="n">
-        <v>92261</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill- SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720390</v>
+        <v>720365</v>
       </c>
       <c r="R3" t="n">
-        <v>7138467</v>
+        <v>7138578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745155</v>
+        <v>122745138</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>92261</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Lill- SÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720365</v>
+        <v>720390</v>
       </c>
       <c r="R4" t="n">
-        <v>7138578</v>
+        <v>7138467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745160</v>
+        <v>122745155</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>79876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorp SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720387</v>
+        <v>720365</v>
       </c>
       <c r="R2" t="n">
-        <v>7138560</v>
+        <v>7138578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745155</v>
+        <v>122745160</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Tjuttorp SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720365</v>
+        <v>720387</v>
       </c>
       <c r="R3" t="n">
-        <v>7138578</v>
+        <v>7138560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122745155</v>
+        <v>122745138</v>
       </c>
       <c r="B2" t="n">
-        <v>79876</v>
+        <v>92264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Lill- SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720365</v>
+        <v>720390</v>
       </c>
       <c r="R2" t="n">
-        <v>7138578</v>
+        <v>7138467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122745160</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745138</v>
+        <v>122745155</v>
       </c>
       <c r="B4" t="n">
-        <v>92261</v>
+        <v>79879</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill- SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720390</v>
+        <v>720365</v>
       </c>
       <c r="R4" t="n">
-        <v>7138467</v>
+        <v>7138578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42588-2024 artfynd.xlsx
+++ b/artfynd/A 42588-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122745138</v>
       </c>
       <c r="B2" t="n">
-        <v>92264</v>
+        <v>92266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122745160</v>
+        <v>122745155</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>79881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjuttorp SÖ, Vb</t>
+          <t>Tjuttorp Ö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720387</v>
+        <v>720365</v>
       </c>
       <c r="R3" t="n">
-        <v>7138560</v>
+        <v>7138578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122745155</v>
+        <v>122745160</v>
       </c>
       <c r="B4" t="n">
-        <v>79879</v>
+        <v>90975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjuttorp Ö, Vb</t>
+          <t>Tjuttorp SÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720365</v>
+        <v>720387</v>
       </c>
       <c r="R4" t="n">
-        <v>7138578</v>
+        <v>7138560</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
